--- a/logs/feature_importance_analysis/yaw_angle/experiments_summary.xlsx
+++ b/logs/feature_importance_analysis/yaw_angle/experiments_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BX51"/>
+  <dimension ref="A1:BX81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11810,6 +11810,6606 @@
         <v>-3.526621576694502</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>15/04/2026 23:18:16</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>04-15_23-18-16_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>5</v>
+      </c>
+      <c r="K52" t="n">
+        <v>5</v>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M52" t="b">
+        <v>1</v>
+      </c>
+      <c r="N52" t="b">
+        <v>0</v>
+      </c>
+      <c r="O52" t="b">
+        <v>0</v>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R52" t="n">
+        <v>1</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z52" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB52" t="inlineStr"/>
+      <c r="AC52" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE52" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG52" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0.0571507303283527</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>5.26290894248401</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0.984220758209728</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>-3.637001257085258</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>8.188828940393707</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>0.9766931493118436</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>8.188828940393707</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>8.188828940393707</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>0.9766931493118436</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>1570.873387538808</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>-3.470982573926532</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr"/>
+      <c r="AX52" t="inlineStr"/>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr"/>
+      <c r="BA52" t="inlineStr"/>
+      <c r="BB52" t="inlineStr"/>
+      <c r="BC52" t="inlineStr"/>
+      <c r="BD52" t="inlineStr"/>
+      <c r="BE52" t="inlineStr"/>
+      <c r="BF52" t="inlineStr"/>
+      <c r="BG52" t="inlineStr"/>
+      <c r="BH52" t="inlineStr"/>
+      <c r="BI52" t="inlineStr"/>
+      <c r="BJ52" t="inlineStr"/>
+      <c r="BK52" t="inlineStr"/>
+      <c r="BL52" t="inlineStr"/>
+      <c r="BM52" t="inlineStr"/>
+      <c r="BN52" t="inlineStr"/>
+      <c r="BO52" t="inlineStr"/>
+      <c r="BP52" t="inlineStr"/>
+      <c r="BQ52" t="inlineStr"/>
+      <c r="BR52" t="n">
+        <v>8.188828940393707</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>0.9766931493118436</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>8.188828940393707</v>
+      </c>
+      <c r="BU52" t="n">
+        <v>8.188828940393707</v>
+      </c>
+      <c r="BV52" t="n">
+        <v>0.9766931493118436</v>
+      </c>
+      <c r="BW52" t="n">
+        <v>1570.873387538808</v>
+      </c>
+      <c r="BX52" t="n">
+        <v>-3.470982573926532</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>15/04/2026 23:39:40</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>04-15_23-39-40_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G53" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>5</v>
+      </c>
+      <c r="K53" t="n">
+        <v>5</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M53" t="b">
+        <v>1</v>
+      </c>
+      <c r="N53" t="b">
+        <v>0</v>
+      </c>
+      <c r="O53" t="b">
+        <v>0</v>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R53" t="n">
+        <v>1</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z53" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB53" t="inlineStr"/>
+      <c r="AC53" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE53" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG53" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0.0742763024892806</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>5.32380974050532</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0.9840381655736592</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>-3.851288629086025</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>8.053517815939047</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0.9770782686246374</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>8.053517815939047</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>8.053517815939047</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>0.9770782686246374</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>1637.072353795796</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>-3.659396501423686</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr"/>
+      <c r="AX53" t="inlineStr"/>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr"/>
+      <c r="BA53" t="inlineStr"/>
+      <c r="BB53" t="inlineStr"/>
+      <c r="BC53" t="inlineStr"/>
+      <c r="BD53" t="inlineStr"/>
+      <c r="BE53" t="inlineStr"/>
+      <c r="BF53" t="inlineStr"/>
+      <c r="BG53" t="inlineStr"/>
+      <c r="BH53" t="inlineStr"/>
+      <c r="BI53" t="inlineStr"/>
+      <c r="BJ53" t="inlineStr"/>
+      <c r="BK53" t="inlineStr"/>
+      <c r="BL53" t="inlineStr"/>
+      <c r="BM53" t="inlineStr"/>
+      <c r="BN53" t="inlineStr"/>
+      <c r="BO53" t="inlineStr"/>
+      <c r="BP53" t="inlineStr"/>
+      <c r="BQ53" t="inlineStr"/>
+      <c r="BR53" t="n">
+        <v>8.053517815939047</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>0.9770782686246374</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>8.053517815939047</v>
+      </c>
+      <c r="BU53" t="n">
+        <v>8.053517815939047</v>
+      </c>
+      <c r="BV53" t="n">
+        <v>0.9770782686246374</v>
+      </c>
+      <c r="BW53" t="n">
+        <v>1637.072353795796</v>
+      </c>
+      <c r="BX53" t="n">
+        <v>-3.659396501423686</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>15/04/2026 23:40:19</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>04-15_23-40-19_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>5</v>
+      </c>
+      <c r="K54" t="n">
+        <v>5</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M54" t="b">
+        <v>1</v>
+      </c>
+      <c r="N54" t="b">
+        <v>0</v>
+      </c>
+      <c r="O54" t="b">
+        <v>0</v>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R54" t="n">
+        <v>1</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z54" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB54" t="inlineStr"/>
+      <c r="AC54" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE54" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0.0516040373591948</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>4.983463378453373</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0.9850585912732006</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>-3.754845137846113</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>7.716047078567998</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>0.9780387698324148</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>7.716047078567998</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>7.716047078567998</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>0.9780387698324148</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>1609.016107596303</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>-3.579543478995024</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr"/>
+      <c r="AX54" t="inlineStr"/>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr"/>
+      <c r="BA54" t="inlineStr"/>
+      <c r="BB54" t="inlineStr"/>
+      <c r="BC54" t="inlineStr"/>
+      <c r="BD54" t="inlineStr"/>
+      <c r="BE54" t="inlineStr"/>
+      <c r="BF54" t="inlineStr"/>
+      <c r="BG54" t="inlineStr"/>
+      <c r="BH54" t="inlineStr"/>
+      <c r="BI54" t="inlineStr"/>
+      <c r="BJ54" t="inlineStr"/>
+      <c r="BK54" t="inlineStr"/>
+      <c r="BL54" t="inlineStr"/>
+      <c r="BM54" t="inlineStr"/>
+      <c r="BN54" t="inlineStr"/>
+      <c r="BO54" t="inlineStr"/>
+      <c r="BP54" t="inlineStr"/>
+      <c r="BQ54" t="inlineStr"/>
+      <c r="BR54" t="n">
+        <v>7.716047078567998</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>0.9780387698324148</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>7.716047078567998</v>
+      </c>
+      <c r="BU54" t="n">
+        <v>7.716047078567998</v>
+      </c>
+      <c r="BV54" t="n">
+        <v>0.9780387698324148</v>
+      </c>
+      <c r="BW54" t="n">
+        <v>1609.016107596303</v>
+      </c>
+      <c r="BX54" t="n">
+        <v>-3.579543478995024</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>15/04/2026 23:59:38</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>04-15_23-59-38_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>3</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G55" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>5</v>
+      </c>
+      <c r="K55" t="n">
+        <v>5</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M55" t="b">
+        <v>1</v>
+      </c>
+      <c r="N55" t="b">
+        <v>0</v>
+      </c>
+      <c r="O55" t="b">
+        <v>0</v>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R55" t="n">
+        <v>1</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z55" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB55" t="inlineStr"/>
+      <c r="AC55" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE55" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG55" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0.051529209445482</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>5.680751893053137</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0.982967982412266</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>-3.639589021567774</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>8.353043958365772</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>0.9762257644229312</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>8.353043958365772</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>8.353043958365772</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>0.9762257644229312</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>1571.459982038853</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>-3.472652125278328</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr"/>
+      <c r="AX55" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr"/>
+      <c r="BA55" t="inlineStr"/>
+      <c r="BB55" t="inlineStr"/>
+      <c r="BC55" t="inlineStr"/>
+      <c r="BD55" t="inlineStr"/>
+      <c r="BE55" t="inlineStr"/>
+      <c r="BF55" t="inlineStr"/>
+      <c r="BG55" t="inlineStr"/>
+      <c r="BH55" t="inlineStr"/>
+      <c r="BI55" t="inlineStr"/>
+      <c r="BJ55" t="inlineStr"/>
+      <c r="BK55" t="inlineStr"/>
+      <c r="BL55" t="inlineStr"/>
+      <c r="BM55" t="inlineStr"/>
+      <c r="BN55" t="inlineStr"/>
+      <c r="BO55" t="inlineStr"/>
+      <c r="BP55" t="inlineStr"/>
+      <c r="BQ55" t="inlineStr"/>
+      <c r="BR55" t="n">
+        <v>8.353043958365772</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>0.9762257644229312</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>8.353043958365772</v>
+      </c>
+      <c r="BU55" t="n">
+        <v>8.353043958365772</v>
+      </c>
+      <c r="BV55" t="n">
+        <v>0.9762257644229312</v>
+      </c>
+      <c r="BW55" t="n">
+        <v>1571.459982038853</v>
+      </c>
+      <c r="BX55" t="n">
+        <v>-3.472652125278328</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>16/04/2026 00:20:53</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>04-16_00-20-53_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>4</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>5</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M56" t="b">
+        <v>1</v>
+      </c>
+      <c r="N56" t="b">
+        <v>0</v>
+      </c>
+      <c r="O56" t="b">
+        <v>0</v>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R56" t="n">
+        <v>1</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X56" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z56" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB56" t="inlineStr"/>
+      <c r="AC56" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE56" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG56" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH56" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI56" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ56" t="n">
+        <v>0.0323613510239141</v>
+      </c>
+      <c r="AK56" t="n">
+        <v>6.134623838021901</v>
+      </c>
+      <c r="AL56" t="n">
+        <v>0.9816071845645832</v>
+      </c>
+      <c r="AM56" t="n">
+        <v>-3.804297484629116</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>9.201614723969168</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>0.9738105824382772</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>9.201614723969168</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>9.201614723969168</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>0.9738105824382772</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>1624.510217131808</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>-3.623642446029081</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr"/>
+      <c r="AX56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr"/>
+      <c r="BA56" t="inlineStr"/>
+      <c r="BB56" t="inlineStr"/>
+      <c r="BC56" t="inlineStr"/>
+      <c r="BD56" t="inlineStr"/>
+      <c r="BE56" t="inlineStr"/>
+      <c r="BF56" t="inlineStr"/>
+      <c r="BG56" t="inlineStr"/>
+      <c r="BH56" t="inlineStr"/>
+      <c r="BI56" t="inlineStr"/>
+      <c r="BJ56" t="inlineStr"/>
+      <c r="BK56" t="inlineStr"/>
+      <c r="BL56" t="inlineStr"/>
+      <c r="BM56" t="inlineStr"/>
+      <c r="BN56" t="inlineStr"/>
+      <c r="BO56" t="inlineStr"/>
+      <c r="BP56" t="inlineStr"/>
+      <c r="BQ56" t="inlineStr"/>
+      <c r="BR56" t="n">
+        <v>9.201614723969168</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>0.9738105824382772</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>9.201614723969168</v>
+      </c>
+      <c r="BU56" t="n">
+        <v>9.201614723969168</v>
+      </c>
+      <c r="BV56" t="n">
+        <v>0.9738105824382772</v>
+      </c>
+      <c r="BW56" t="n">
+        <v>1624.510217131808</v>
+      </c>
+      <c r="BX56" t="n">
+        <v>-3.623642446029081</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>16/04/2026 00:21:27</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>04-16_00-21-27_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G57" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>5</v>
+      </c>
+      <c r="K57" t="n">
+        <v>5</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M57" t="b">
+        <v>1</v>
+      </c>
+      <c r="N57" t="b">
+        <v>0</v>
+      </c>
+      <c r="O57" t="b">
+        <v>0</v>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R57" t="n">
+        <v>1</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z57" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA57" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB57" t="inlineStr"/>
+      <c r="AC57" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE57" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG57" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH57" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI57" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ57" t="n">
+        <v>0.07279895139954649</v>
+      </c>
+      <c r="AK57" t="n">
+        <v>5.33760499111815</v>
+      </c>
+      <c r="AL57" t="n">
+        <v>0.983996804684205</v>
+      </c>
+      <c r="AM57" t="n">
+        <v>-3.667662959479729</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>8.246059278014467</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>0.9765302616824316</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>8.246059278014467</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>8.246059278014467</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>0.9765302616824316</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>1582.088118269746</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>-3.502901674515448</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr"/>
+      <c r="AX57" t="inlineStr"/>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr"/>
+      <c r="BA57" t="inlineStr"/>
+      <c r="BB57" t="inlineStr"/>
+      <c r="BC57" t="inlineStr"/>
+      <c r="BD57" t="inlineStr"/>
+      <c r="BE57" t="inlineStr"/>
+      <c r="BF57" t="inlineStr"/>
+      <c r="BG57" t="inlineStr"/>
+      <c r="BH57" t="inlineStr"/>
+      <c r="BI57" t="inlineStr"/>
+      <c r="BJ57" t="inlineStr"/>
+      <c r="BK57" t="inlineStr"/>
+      <c r="BL57" t="inlineStr"/>
+      <c r="BM57" t="inlineStr"/>
+      <c r="BN57" t="inlineStr"/>
+      <c r="BO57" t="inlineStr"/>
+      <c r="BP57" t="inlineStr"/>
+      <c r="BQ57" t="inlineStr"/>
+      <c r="BR57" t="n">
+        <v>8.246059278014467</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>0.9765302616824316</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>8.246059278014467</v>
+      </c>
+      <c r="BU57" t="n">
+        <v>8.246059278014467</v>
+      </c>
+      <c r="BV57" t="n">
+        <v>0.9765302616824316</v>
+      </c>
+      <c r="BW57" t="n">
+        <v>1582.088118269746</v>
+      </c>
+      <c r="BX57" t="n">
+        <v>-3.502901674515448</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>16/04/2026 00:23:04</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>04-16_00-23-04_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>6</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G58" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>5</v>
+      </c>
+      <c r="K58" t="n">
+        <v>5</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M58" t="b">
+        <v>1</v>
+      </c>
+      <c r="N58" t="b">
+        <v>0</v>
+      </c>
+      <c r="O58" t="b">
+        <v>0</v>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R58" t="n">
+        <v>1</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X58" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z58" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA58" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB58" t="inlineStr"/>
+      <c r="AC58" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE58" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG58" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH58" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI58" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ58" t="n">
+        <v>0.0535248190025933</v>
+      </c>
+      <c r="AK58" t="n">
+        <v>6.412599130980864</v>
+      </c>
+      <c r="AL58" t="n">
+        <v>0.9807737596645409</v>
+      </c>
+      <c r="AM58" t="n">
+        <v>-3.315272679274432</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>10.24059108205731</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>0.9708534725727826</v>
+      </c>
+      <c r="AP58" t="n">
+        <v>10.24059108205731</v>
+      </c>
+      <c r="AQ58" t="n">
+        <v>10.24059108205731</v>
+      </c>
+      <c r="AR58" t="n">
+        <v>0.9708534725727826</v>
+      </c>
+      <c r="AS58" t="n">
+        <v>1471.642037751489</v>
+      </c>
+      <c r="AT58" t="n">
+        <v>-3.188552659965469</v>
+      </c>
+      <c r="AU58" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW58" t="inlineStr"/>
+      <c r="AX58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr"/>
+      <c r="BA58" t="inlineStr"/>
+      <c r="BB58" t="inlineStr"/>
+      <c r="BC58" t="inlineStr"/>
+      <c r="BD58" t="inlineStr"/>
+      <c r="BE58" t="inlineStr"/>
+      <c r="BF58" t="inlineStr"/>
+      <c r="BG58" t="inlineStr"/>
+      <c r="BH58" t="inlineStr"/>
+      <c r="BI58" t="inlineStr"/>
+      <c r="BJ58" t="inlineStr"/>
+      <c r="BK58" t="inlineStr"/>
+      <c r="BL58" t="inlineStr"/>
+      <c r="BM58" t="inlineStr"/>
+      <c r="BN58" t="inlineStr"/>
+      <c r="BO58" t="inlineStr"/>
+      <c r="BP58" t="inlineStr"/>
+      <c r="BQ58" t="inlineStr"/>
+      <c r="BR58" t="n">
+        <v>10.24059108205731</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>0.9708534725727826</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>10.24059108205731</v>
+      </c>
+      <c r="BU58" t="n">
+        <v>10.24059108205731</v>
+      </c>
+      <c r="BV58" t="n">
+        <v>0.9708534725727826</v>
+      </c>
+      <c r="BW58" t="n">
+        <v>1471.642037751489</v>
+      </c>
+      <c r="BX58" t="n">
+        <v>-3.188552659965469</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>16/04/2026 00:23:22</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>04-16_00-23-22_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>7</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G59" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>5</v>
+      </c>
+      <c r="K59" t="n">
+        <v>5</v>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M59" t="b">
+        <v>1</v>
+      </c>
+      <c r="N59" t="b">
+        <v>0</v>
+      </c>
+      <c r="O59" t="b">
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R59" t="n">
+        <v>1</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X59" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z59" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB59" t="inlineStr"/>
+      <c r="AC59" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE59" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG59" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI59" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ59" t="n">
+        <v>0.0553015366484895</v>
+      </c>
+      <c r="AK59" t="n">
+        <v>5.37941035425243</v>
+      </c>
+      <c r="AL59" t="n">
+        <v>0.9838714639381966</v>
+      </c>
+      <c r="AM59" t="n">
+        <v>-3.750350695175582</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>8.229028471551745</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>0.976578734359809</v>
+      </c>
+      <c r="AP59" t="n">
+        <v>8.229028471551745</v>
+      </c>
+      <c r="AQ59" t="n">
+        <v>8.229028471551745</v>
+      </c>
+      <c r="AR59" t="n">
+        <v>0.976578734359809</v>
+      </c>
+      <c r="AS59" t="n">
+        <v>1607.647978196182</v>
+      </c>
+      <c r="AT59" t="n">
+        <v>-3.575649541548924</v>
+      </c>
+      <c r="AU59" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr"/>
+      <c r="AX59" t="inlineStr"/>
+      <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr"/>
+      <c r="BA59" t="inlineStr"/>
+      <c r="BB59" t="inlineStr"/>
+      <c r="BC59" t="inlineStr"/>
+      <c r="BD59" t="inlineStr"/>
+      <c r="BE59" t="inlineStr"/>
+      <c r="BF59" t="inlineStr"/>
+      <c r="BG59" t="inlineStr"/>
+      <c r="BH59" t="inlineStr"/>
+      <c r="BI59" t="inlineStr"/>
+      <c r="BJ59" t="inlineStr"/>
+      <c r="BK59" t="inlineStr"/>
+      <c r="BL59" t="inlineStr"/>
+      <c r="BM59" t="inlineStr"/>
+      <c r="BN59" t="inlineStr"/>
+      <c r="BO59" t="inlineStr"/>
+      <c r="BP59" t="inlineStr"/>
+      <c r="BQ59" t="inlineStr"/>
+      <c r="BR59" t="n">
+        <v>8.229028471551745</v>
+      </c>
+      <c r="BS59" t="n">
+        <v>0.976578734359809</v>
+      </c>
+      <c r="BT59" t="n">
+        <v>8.229028471551745</v>
+      </c>
+      <c r="BU59" t="n">
+        <v>8.229028471551745</v>
+      </c>
+      <c r="BV59" t="n">
+        <v>0.976578734359809</v>
+      </c>
+      <c r="BW59" t="n">
+        <v>1607.647978196182</v>
+      </c>
+      <c r="BX59" t="n">
+        <v>-3.575649541548924</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>16/04/2026 00:41:05</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>04-16_00-41-05_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>8</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G60" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>5</v>
+      </c>
+      <c r="K60" t="n">
+        <v>5</v>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M60" t="b">
+        <v>1</v>
+      </c>
+      <c r="N60" t="b">
+        <v>0</v>
+      </c>
+      <c r="O60" t="b">
+        <v>0</v>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R60" t="n">
+        <v>1</v>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X60" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z60" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB60" t="inlineStr"/>
+      <c r="AC60" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE60" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG60" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>0.0554898157188129</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>5.454617142080172</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>0.9836459791155684</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>-3.640627637349423</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>8.200630290634107</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>0.9766595605887216</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>8.200630290634107</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>8.200630290634107</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>0.9766595605887216</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>1577.740266855822</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>-3.490526922953749</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV60" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW60" t="inlineStr"/>
+      <c r="AX60" t="inlineStr"/>
+      <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr"/>
+      <c r="BA60" t="inlineStr"/>
+      <c r="BB60" t="inlineStr"/>
+      <c r="BC60" t="inlineStr"/>
+      <c r="BD60" t="inlineStr"/>
+      <c r="BE60" t="inlineStr"/>
+      <c r="BF60" t="inlineStr"/>
+      <c r="BG60" t="inlineStr"/>
+      <c r="BH60" t="inlineStr"/>
+      <c r="BI60" t="inlineStr"/>
+      <c r="BJ60" t="inlineStr"/>
+      <c r="BK60" t="inlineStr"/>
+      <c r="BL60" t="inlineStr"/>
+      <c r="BM60" t="inlineStr"/>
+      <c r="BN60" t="inlineStr"/>
+      <c r="BO60" t="inlineStr"/>
+      <c r="BP60" t="inlineStr"/>
+      <c r="BQ60" t="inlineStr"/>
+      <c r="BR60" t="n">
+        <v>8.200630290634107</v>
+      </c>
+      <c r="BS60" t="n">
+        <v>0.9766595605887216</v>
+      </c>
+      <c r="BT60" t="n">
+        <v>8.200630290634107</v>
+      </c>
+      <c r="BU60" t="n">
+        <v>8.200630290634107</v>
+      </c>
+      <c r="BV60" t="n">
+        <v>0.9766595605887216</v>
+      </c>
+      <c r="BW60" t="n">
+        <v>1577.740266855822</v>
+      </c>
+      <c r="BX60" t="n">
+        <v>-3.490526922953749</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>16/04/2026 01:02:07</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>04-16_01-02-07_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r1.pkl</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>9</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G61" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>5</v>
+      </c>
+      <c r="K61" t="n">
+        <v>5</v>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M61" t="b">
+        <v>1</v>
+      </c>
+      <c r="N61" t="b">
+        <v>0</v>
+      </c>
+      <c r="O61" t="b">
+        <v>0</v>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 1, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R61" t="n">
+        <v>1</v>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X61" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z61" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA61" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB61" t="inlineStr"/>
+      <c r="AC61" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE61" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG61" t="n">
+        <v>40</v>
+      </c>
+      <c r="AH61" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI61" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ61" t="n">
+        <v>0.0455307926810092</v>
+      </c>
+      <c r="AK61" t="n">
+        <v>5.198848137849674</v>
+      </c>
+      <c r="AL61" t="n">
+        <v>0.9844128251705384</v>
+      </c>
+      <c r="AM61" t="n">
+        <v>-3.705521951131427</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>7.893586387800513</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>0.977533461661774</v>
+      </c>
+      <c r="AP61" t="n">
+        <v>7.893586387800513</v>
+      </c>
+      <c r="AQ61" t="n">
+        <v>7.893586387800513</v>
+      </c>
+      <c r="AR61" t="n">
+        <v>0.977533461661774</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>1591.074277294965</v>
+      </c>
+      <c r="AT61" t="n">
+        <v>-3.528477867178077</v>
+      </c>
+      <c r="AU61" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV61" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr"/>
+      <c r="AX61" t="inlineStr"/>
+      <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr"/>
+      <c r="BA61" t="inlineStr"/>
+      <c r="BB61" t="inlineStr"/>
+      <c r="BC61" t="inlineStr"/>
+      <c r="BD61" t="inlineStr"/>
+      <c r="BE61" t="inlineStr"/>
+      <c r="BF61" t="inlineStr"/>
+      <c r="BG61" t="inlineStr"/>
+      <c r="BH61" t="inlineStr"/>
+      <c r="BI61" t="inlineStr"/>
+      <c r="BJ61" t="inlineStr"/>
+      <c r="BK61" t="inlineStr"/>
+      <c r="BL61" t="inlineStr"/>
+      <c r="BM61" t="inlineStr"/>
+      <c r="BN61" t="inlineStr"/>
+      <c r="BO61" t="inlineStr"/>
+      <c r="BP61" t="inlineStr"/>
+      <c r="BQ61" t="inlineStr"/>
+      <c r="BR61" t="n">
+        <v>7.893586387800513</v>
+      </c>
+      <c r="BS61" t="n">
+        <v>0.977533461661774</v>
+      </c>
+      <c r="BT61" t="n">
+        <v>7.893586387800513</v>
+      </c>
+      <c r="BU61" t="n">
+        <v>7.893586387800513</v>
+      </c>
+      <c r="BV61" t="n">
+        <v>0.977533461661774</v>
+      </c>
+      <c r="BW61" t="n">
+        <v>1591.074277294965</v>
+      </c>
+      <c r="BX61" t="n">
+        <v>-3.528477867178077</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>16/04/2026 01:02:59</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>04-16_01-02-59_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G62" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>5</v>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M62" t="b">
+        <v>1</v>
+      </c>
+      <c r="N62" t="b">
+        <v>0</v>
+      </c>
+      <c r="O62" t="b">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R62" t="n">
+        <v>1</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V62" t="n">
+        <v>3</v>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X62" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z62" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA62" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB62" t="inlineStr"/>
+      <c r="AC62" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE62" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG62" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH62" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI62" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ62" t="n">
+        <v>0.0433843094755309</v>
+      </c>
+      <c r="AK62" t="n">
+        <v>7.268983064218859</v>
+      </c>
+      <c r="AL62" t="n">
+        <v>0.9782061512761868</v>
+      </c>
+      <c r="AM62" t="n">
+        <v>-0.527693694521628</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>10.9340548814811</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>0.9688797523560756</v>
+      </c>
+      <c r="AP62" t="n">
+        <v>10.9340548814811</v>
+      </c>
+      <c r="AQ62" t="n">
+        <v>10.9340548814811</v>
+      </c>
+      <c r="AR62" t="n">
+        <v>0.9688797523560756</v>
+      </c>
+      <c r="AS62" t="n">
+        <v>542.3749152537223</v>
+      </c>
+      <c r="AT62" t="n">
+        <v>-0.5436946184654647</v>
+      </c>
+      <c r="AU62" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr"/>
+      <c r="AX62" t="inlineStr"/>
+      <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr"/>
+      <c r="BA62" t="inlineStr"/>
+      <c r="BB62" t="inlineStr"/>
+      <c r="BC62" t="inlineStr"/>
+      <c r="BD62" t="inlineStr"/>
+      <c r="BE62" t="inlineStr"/>
+      <c r="BF62" t="inlineStr"/>
+      <c r="BG62" t="inlineStr"/>
+      <c r="BH62" t="inlineStr"/>
+      <c r="BI62" t="inlineStr"/>
+      <c r="BJ62" t="inlineStr"/>
+      <c r="BK62" t="inlineStr"/>
+      <c r="BL62" t="inlineStr"/>
+      <c r="BM62" t="inlineStr"/>
+      <c r="BN62" t="inlineStr"/>
+      <c r="BO62" t="inlineStr"/>
+      <c r="BP62" t="inlineStr"/>
+      <c r="BQ62" t="inlineStr"/>
+      <c r="BR62" t="n">
+        <v>10.9340548814811</v>
+      </c>
+      <c r="BS62" t="n">
+        <v>0.9688797523560756</v>
+      </c>
+      <c r="BT62" t="n">
+        <v>10.9340548814811</v>
+      </c>
+      <c r="BU62" t="n">
+        <v>10.9340548814811</v>
+      </c>
+      <c r="BV62" t="n">
+        <v>0.9688797523560756</v>
+      </c>
+      <c r="BW62" t="n">
+        <v>542.3749152537223</v>
+      </c>
+      <c r="BX62" t="n">
+        <v>-0.5436946184654647</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>16/04/2026 01:07:41</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>04-16_01-07-41_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G63" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>5</v>
+      </c>
+      <c r="K63" t="n">
+        <v>5</v>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M63" t="b">
+        <v>1</v>
+      </c>
+      <c r="N63" t="b">
+        <v>0</v>
+      </c>
+      <c r="O63" t="b">
+        <v>0</v>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R63" t="n">
+        <v>1</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V63" t="n">
+        <v>3</v>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X63" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z63" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB63" t="inlineStr"/>
+      <c r="AC63" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE63" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG63" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>0.0474379904339475</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>8.58393155426303</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>0.974263675661861</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>-0.5748094057550592</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>15.44985057966474</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>0.9560270017562168</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>15.44985057966474</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>15.44985057966474</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>0.9560270017562168</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>547.2682531435236</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>-0.5576219206956678</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr"/>
+      <c r="AX63" t="inlineStr"/>
+      <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr"/>
+      <c r="BA63" t="inlineStr"/>
+      <c r="BB63" t="inlineStr"/>
+      <c r="BC63" t="inlineStr"/>
+      <c r="BD63" t="inlineStr"/>
+      <c r="BE63" t="inlineStr"/>
+      <c r="BF63" t="inlineStr"/>
+      <c r="BG63" t="inlineStr"/>
+      <c r="BH63" t="inlineStr"/>
+      <c r="BI63" t="inlineStr"/>
+      <c r="BJ63" t="inlineStr"/>
+      <c r="BK63" t="inlineStr"/>
+      <c r="BL63" t="inlineStr"/>
+      <c r="BM63" t="inlineStr"/>
+      <c r="BN63" t="inlineStr"/>
+      <c r="BO63" t="inlineStr"/>
+      <c r="BP63" t="inlineStr"/>
+      <c r="BQ63" t="inlineStr"/>
+      <c r="BR63" t="n">
+        <v>15.44985057966474</v>
+      </c>
+      <c r="BS63" t="n">
+        <v>0.9560270017562168</v>
+      </c>
+      <c r="BT63" t="n">
+        <v>15.44985057966474</v>
+      </c>
+      <c r="BU63" t="n">
+        <v>15.44985057966474</v>
+      </c>
+      <c r="BV63" t="n">
+        <v>0.9560270017562168</v>
+      </c>
+      <c r="BW63" t="n">
+        <v>547.2682531435236</v>
+      </c>
+      <c r="BX63" t="n">
+        <v>-0.5576219206956678</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>16/04/2026 01:07:50</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>04-16_01-07-50_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G64" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>5</v>
+      </c>
+      <c r="K64" t="n">
+        <v>5</v>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M64" t="b">
+        <v>1</v>
+      </c>
+      <c r="N64" t="b">
+        <v>0</v>
+      </c>
+      <c r="O64" t="b">
+        <v>0</v>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R64" t="n">
+        <v>1</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V64" t="n">
+        <v>3</v>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X64" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z64" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA64" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB64" t="inlineStr"/>
+      <c r="AC64" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE64" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG64" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH64" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI64" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ64" t="n">
+        <v>0.044807172623617</v>
+      </c>
+      <c r="AK64" t="n">
+        <v>13.49298940399798</v>
+      </c>
+      <c r="AL64" t="n">
+        <v>0.9595453494244248</v>
+      </c>
+      <c r="AM64" t="n">
+        <v>-0.3843683458690434</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>17.85001409812087</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>0.949195713282736</v>
+      </c>
+      <c r="AP64" t="n">
+        <v>17.85001409812087</v>
+      </c>
+      <c r="AQ64" t="n">
+        <v>17.85001409812087</v>
+      </c>
+      <c r="AR64" t="n">
+        <v>0.949195713282736</v>
+      </c>
+      <c r="AS64" t="n">
+        <v>472.5954328610288</v>
+      </c>
+      <c r="AT64" t="n">
+        <v>-0.3450899108740082</v>
+      </c>
+      <c r="AU64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr"/>
+      <c r="AX64" t="inlineStr"/>
+      <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr"/>
+      <c r="BA64" t="inlineStr"/>
+      <c r="BB64" t="inlineStr"/>
+      <c r="BC64" t="inlineStr"/>
+      <c r="BD64" t="inlineStr"/>
+      <c r="BE64" t="inlineStr"/>
+      <c r="BF64" t="inlineStr"/>
+      <c r="BG64" t="inlineStr"/>
+      <c r="BH64" t="inlineStr"/>
+      <c r="BI64" t="inlineStr"/>
+      <c r="BJ64" t="inlineStr"/>
+      <c r="BK64" t="inlineStr"/>
+      <c r="BL64" t="inlineStr"/>
+      <c r="BM64" t="inlineStr"/>
+      <c r="BN64" t="inlineStr"/>
+      <c r="BO64" t="inlineStr"/>
+      <c r="BP64" t="inlineStr"/>
+      <c r="BQ64" t="inlineStr"/>
+      <c r="BR64" t="n">
+        <v>17.85001409812087</v>
+      </c>
+      <c r="BS64" t="n">
+        <v>0.949195713282736</v>
+      </c>
+      <c r="BT64" t="n">
+        <v>17.85001409812087</v>
+      </c>
+      <c r="BU64" t="n">
+        <v>17.85001409812087</v>
+      </c>
+      <c r="BV64" t="n">
+        <v>0.949195713282736</v>
+      </c>
+      <c r="BW64" t="n">
+        <v>472.5954328610288</v>
+      </c>
+      <c r="BX64" t="n">
+        <v>-0.3450899108740082</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>16/04/2026 01:22:18</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>04-16_01-22-18_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>3</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G65" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>5</v>
+      </c>
+      <c r="K65" t="n">
+        <v>5</v>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M65" t="b">
+        <v>1</v>
+      </c>
+      <c r="N65" t="b">
+        <v>0</v>
+      </c>
+      <c r="O65" t="b">
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R65" t="n">
+        <v>1</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V65" t="n">
+        <v>3</v>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X65" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z65" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB65" t="inlineStr"/>
+      <c r="AC65" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE65" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG65" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ65" t="n">
+        <v>0.0419660558575232</v>
+      </c>
+      <c r="AK65" t="n">
+        <v>7.744057795057873</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>0.9767817832834508</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>-1.031093127735195</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>10.43612768758244</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>0.9702969409243364</v>
+      </c>
+      <c r="AP65" t="n">
+        <v>10.43612768758244</v>
+      </c>
+      <c r="AQ65" t="n">
+        <v>10.43612768758244</v>
+      </c>
+      <c r="AR65" t="n">
+        <v>0.9702969409243364</v>
+      </c>
+      <c r="AS65" t="n">
+        <v>690.8727473110533</v>
+      </c>
+      <c r="AT65" t="n">
+        <v>-0.966345625644612</v>
+      </c>
+      <c r="AU65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr"/>
+      <c r="AX65" t="inlineStr"/>
+      <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr"/>
+      <c r="BA65" t="inlineStr"/>
+      <c r="BB65" t="inlineStr"/>
+      <c r="BC65" t="inlineStr"/>
+      <c r="BD65" t="inlineStr"/>
+      <c r="BE65" t="inlineStr"/>
+      <c r="BF65" t="inlineStr"/>
+      <c r="BG65" t="inlineStr"/>
+      <c r="BH65" t="inlineStr"/>
+      <c r="BI65" t="inlineStr"/>
+      <c r="BJ65" t="inlineStr"/>
+      <c r="BK65" t="inlineStr"/>
+      <c r="BL65" t="inlineStr"/>
+      <c r="BM65" t="inlineStr"/>
+      <c r="BN65" t="inlineStr"/>
+      <c r="BO65" t="inlineStr"/>
+      <c r="BP65" t="inlineStr"/>
+      <c r="BQ65" t="inlineStr"/>
+      <c r="BR65" t="n">
+        <v>10.43612768758244</v>
+      </c>
+      <c r="BS65" t="n">
+        <v>0.9702969409243364</v>
+      </c>
+      <c r="BT65" t="n">
+        <v>10.43612768758244</v>
+      </c>
+      <c r="BU65" t="n">
+        <v>10.43612768758244</v>
+      </c>
+      <c r="BV65" t="n">
+        <v>0.9702969409243364</v>
+      </c>
+      <c r="BW65" t="n">
+        <v>690.8727473110533</v>
+      </c>
+      <c r="BX65" t="n">
+        <v>-0.966345625644612</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>16/04/2026 01:43:21</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>04-16_01-43-21_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>4</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G66" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>5</v>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M66" t="b">
+        <v>1</v>
+      </c>
+      <c r="N66" t="b">
+        <v>0</v>
+      </c>
+      <c r="O66" t="b">
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R66" t="n">
+        <v>1</v>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V66" t="n">
+        <v>3</v>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X66" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z66" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB66" t="inlineStr"/>
+      <c r="AC66" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE66" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG66" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>0.0497626334387502</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>13.84074964185558</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>0.9585026954590672</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>-0.383095584435577</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>17.93686022239851</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>0.9489485339038386</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>17.93686022239851</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>17.93686022239851</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>0.9489485339038386</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>482.1505087828082</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>-0.3722853413127105</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr"/>
+      <c r="AX66" t="inlineStr"/>
+      <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr"/>
+      <c r="BA66" t="inlineStr"/>
+      <c r="BB66" t="inlineStr"/>
+      <c r="BC66" t="inlineStr"/>
+      <c r="BD66" t="inlineStr"/>
+      <c r="BE66" t="inlineStr"/>
+      <c r="BF66" t="inlineStr"/>
+      <c r="BG66" t="inlineStr"/>
+      <c r="BH66" t="inlineStr"/>
+      <c r="BI66" t="inlineStr"/>
+      <c r="BJ66" t="inlineStr"/>
+      <c r="BK66" t="inlineStr"/>
+      <c r="BL66" t="inlineStr"/>
+      <c r="BM66" t="inlineStr"/>
+      <c r="BN66" t="inlineStr"/>
+      <c r="BO66" t="inlineStr"/>
+      <c r="BP66" t="inlineStr"/>
+      <c r="BQ66" t="inlineStr"/>
+      <c r="BR66" t="n">
+        <v>17.93686022239851</v>
+      </c>
+      <c r="BS66" t="n">
+        <v>0.9489485339038386</v>
+      </c>
+      <c r="BT66" t="n">
+        <v>17.93686022239851</v>
+      </c>
+      <c r="BU66" t="n">
+        <v>17.93686022239851</v>
+      </c>
+      <c r="BV66" t="n">
+        <v>0.9489485339038386</v>
+      </c>
+      <c r="BW66" t="n">
+        <v>482.1505087828082</v>
+      </c>
+      <c r="BX66" t="n">
+        <v>-0.3722853413127105</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>16/04/2026 02:04:53</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>04-16_02-04-53_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G67" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>5</v>
+      </c>
+      <c r="K67" t="n">
+        <v>5</v>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M67" t="b">
+        <v>1</v>
+      </c>
+      <c r="N67" t="b">
+        <v>0</v>
+      </c>
+      <c r="O67" t="b">
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R67" t="n">
+        <v>1</v>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V67" t="n">
+        <v>3</v>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X67" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z67" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA67" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB67" t="inlineStr"/>
+      <c r="AC67" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE67" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG67" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI67" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ67" t="n">
+        <v>0.052988112802634</v>
+      </c>
+      <c r="AK67" t="n">
+        <v>12.02885377924304</v>
+      </c>
+      <c r="AL67" t="n">
+        <v>0.9639351175715162</v>
+      </c>
+      <c r="AM67" t="n">
+        <v>-0.450349894424694</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>15.05669291102788</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>0.9571459977868484</v>
+      </c>
+      <c r="AP67" t="n">
+        <v>15.05669291102788</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>15.05669291102788</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>0.9571459977868484</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>505.0679537630975</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>-0.4375124296055042</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr"/>
+      <c r="AX67" t="inlineStr"/>
+      <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr"/>
+      <c r="BA67" t="inlineStr"/>
+      <c r="BB67" t="inlineStr"/>
+      <c r="BC67" t="inlineStr"/>
+      <c r="BD67" t="inlineStr"/>
+      <c r="BE67" t="inlineStr"/>
+      <c r="BF67" t="inlineStr"/>
+      <c r="BG67" t="inlineStr"/>
+      <c r="BH67" t="inlineStr"/>
+      <c r="BI67" t="inlineStr"/>
+      <c r="BJ67" t="inlineStr"/>
+      <c r="BK67" t="inlineStr"/>
+      <c r="BL67" t="inlineStr"/>
+      <c r="BM67" t="inlineStr"/>
+      <c r="BN67" t="inlineStr"/>
+      <c r="BO67" t="inlineStr"/>
+      <c r="BP67" t="inlineStr"/>
+      <c r="BQ67" t="inlineStr"/>
+      <c r="BR67" t="n">
+        <v>15.05669291102788</v>
+      </c>
+      <c r="BS67" t="n">
+        <v>0.9571459977868484</v>
+      </c>
+      <c r="BT67" t="n">
+        <v>15.05669291102788</v>
+      </c>
+      <c r="BU67" t="n">
+        <v>15.05669291102788</v>
+      </c>
+      <c r="BV67" t="n">
+        <v>0.9571459977868484</v>
+      </c>
+      <c r="BW67" t="n">
+        <v>505.0679537630975</v>
+      </c>
+      <c r="BX67" t="n">
+        <v>-0.4375124296055042</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>16/04/2026 02:13:51</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>04-16_02-13-51_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>6</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G68" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>5</v>
+      </c>
+      <c r="K68" t="n">
+        <v>5</v>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M68" t="b">
+        <v>1</v>
+      </c>
+      <c r="N68" t="b">
+        <v>0</v>
+      </c>
+      <c r="O68" t="b">
+        <v>0</v>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R68" t="n">
+        <v>1</v>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V68" t="n">
+        <v>3</v>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X68" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z68" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB68" t="inlineStr"/>
+      <c r="AC68" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE68" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG68" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>0.0436725582096688</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>10.30723919180966</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>0.969096858567162</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>-0.7314887171856255</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>14.14405982376111</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>0.9597435124318394</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>14.14405982376111</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>14.14405982376111</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>0.9597435124318394</v>
+      </c>
+      <c r="AS68" t="n">
+        <v>609.1818643781523</v>
+      </c>
+      <c r="AT68" t="n">
+        <v>-0.7338389723783572</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr"/>
+      <c r="AX68" t="inlineStr"/>
+      <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr"/>
+      <c r="BA68" t="inlineStr"/>
+      <c r="BB68" t="inlineStr"/>
+      <c r="BC68" t="inlineStr"/>
+      <c r="BD68" t="inlineStr"/>
+      <c r="BE68" t="inlineStr"/>
+      <c r="BF68" t="inlineStr"/>
+      <c r="BG68" t="inlineStr"/>
+      <c r="BH68" t="inlineStr"/>
+      <c r="BI68" t="inlineStr"/>
+      <c r="BJ68" t="inlineStr"/>
+      <c r="BK68" t="inlineStr"/>
+      <c r="BL68" t="inlineStr"/>
+      <c r="BM68" t="inlineStr"/>
+      <c r="BN68" t="inlineStr"/>
+      <c r="BO68" t="inlineStr"/>
+      <c r="BP68" t="inlineStr"/>
+      <c r="BQ68" t="inlineStr"/>
+      <c r="BR68" t="n">
+        <v>14.14405982376111</v>
+      </c>
+      <c r="BS68" t="n">
+        <v>0.9597435124318394</v>
+      </c>
+      <c r="BT68" t="n">
+        <v>14.14405982376111</v>
+      </c>
+      <c r="BU68" t="n">
+        <v>14.14405982376111</v>
+      </c>
+      <c r="BV68" t="n">
+        <v>0.9597435124318394</v>
+      </c>
+      <c r="BW68" t="n">
+        <v>609.1818643781523</v>
+      </c>
+      <c r="BX68" t="n">
+        <v>-0.7338389723783572</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>16/04/2026 02:14:15</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>04-16_02-14-15_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>7</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G69" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>5</v>
+      </c>
+      <c r="K69" t="n">
+        <v>5</v>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M69" t="b">
+        <v>1</v>
+      </c>
+      <c r="N69" t="b">
+        <v>0</v>
+      </c>
+      <c r="O69" t="b">
+        <v>0</v>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R69" t="n">
+        <v>1</v>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V69" t="n">
+        <v>3</v>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X69" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z69" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA69" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB69" t="inlineStr"/>
+      <c r="AC69" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE69" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG69" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH69" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI69" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ69" t="n">
+        <v>0.0520302137515374</v>
+      </c>
+      <c r="AK69" t="n">
+        <v>8.877156285501808</v>
+      </c>
+      <c r="AL69" t="n">
+        <v>0.9733845299301622</v>
+      </c>
+      <c r="AM69" t="n">
+        <v>-0.229332839329825</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>12.28857080051313</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>0.9650245612769354</v>
+      </c>
+      <c r="AP69" t="n">
+        <v>12.28857080051313</v>
+      </c>
+      <c r="AQ69" t="n">
+        <v>12.28857080051313</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>0.9650245612769354</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>445.8250219627814</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>-0.2688966023792707</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr"/>
+      <c r="AX69" t="inlineStr"/>
+      <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr"/>
+      <c r="BA69" t="inlineStr"/>
+      <c r="BB69" t="inlineStr"/>
+      <c r="BC69" t="inlineStr"/>
+      <c r="BD69" t="inlineStr"/>
+      <c r="BE69" t="inlineStr"/>
+      <c r="BF69" t="inlineStr"/>
+      <c r="BG69" t="inlineStr"/>
+      <c r="BH69" t="inlineStr"/>
+      <c r="BI69" t="inlineStr"/>
+      <c r="BJ69" t="inlineStr"/>
+      <c r="BK69" t="inlineStr"/>
+      <c r="BL69" t="inlineStr"/>
+      <c r="BM69" t="inlineStr"/>
+      <c r="BN69" t="inlineStr"/>
+      <c r="BO69" t="inlineStr"/>
+      <c r="BP69" t="inlineStr"/>
+      <c r="BQ69" t="inlineStr"/>
+      <c r="BR69" t="n">
+        <v>12.28857080051313</v>
+      </c>
+      <c r="BS69" t="n">
+        <v>0.9650245612769354</v>
+      </c>
+      <c r="BT69" t="n">
+        <v>12.28857080051313</v>
+      </c>
+      <c r="BU69" t="n">
+        <v>12.28857080051313</v>
+      </c>
+      <c r="BV69" t="n">
+        <v>0.9650245612769354</v>
+      </c>
+      <c r="BW69" t="n">
+        <v>445.8250219627814</v>
+      </c>
+      <c r="BX69" t="n">
+        <v>-0.2688966023792707</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>16/04/2026 02:24:01</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>04-16_02-24-01_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>8</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G70" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>5</v>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M70" t="b">
+        <v>1</v>
+      </c>
+      <c r="N70" t="b">
+        <v>0</v>
+      </c>
+      <c r="O70" t="b">
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R70" t="n">
+        <v>1</v>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V70" t="n">
+        <v>3</v>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X70" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z70" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB70" t="inlineStr"/>
+      <c r="AC70" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE70" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG70" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ70" t="n">
+        <v>0.0639734579007652</v>
+      </c>
+      <c r="AK70" t="n">
+        <v>9.824606934133747</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>0.9705438855199138</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>-0.0505746163770708</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>13.89728103216176</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>0.960445888374807</v>
+      </c>
+      <c r="AP70" t="n">
+        <v>13.89728103216176</v>
+      </c>
+      <c r="AQ70" t="n">
+        <v>13.89728103216176</v>
+      </c>
+      <c r="AR70" t="n">
+        <v>0.960445888374807</v>
+      </c>
+      <c r="AS70" t="n">
+        <v>373.6972710510069</v>
+      </c>
+      <c r="AT70" t="n">
+        <v>-0.0636083086305867</v>
+      </c>
+      <c r="AU70" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV70" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW70" t="inlineStr"/>
+      <c r="AX70" t="inlineStr"/>
+      <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr"/>
+      <c r="BA70" t="inlineStr"/>
+      <c r="BB70" t="inlineStr"/>
+      <c r="BC70" t="inlineStr"/>
+      <c r="BD70" t="inlineStr"/>
+      <c r="BE70" t="inlineStr"/>
+      <c r="BF70" t="inlineStr"/>
+      <c r="BG70" t="inlineStr"/>
+      <c r="BH70" t="inlineStr"/>
+      <c r="BI70" t="inlineStr"/>
+      <c r="BJ70" t="inlineStr"/>
+      <c r="BK70" t="inlineStr"/>
+      <c r="BL70" t="inlineStr"/>
+      <c r="BM70" t="inlineStr"/>
+      <c r="BN70" t="inlineStr"/>
+      <c r="BO70" t="inlineStr"/>
+      <c r="BP70" t="inlineStr"/>
+      <c r="BQ70" t="inlineStr"/>
+      <c r="BR70" t="n">
+        <v>13.89728103216176</v>
+      </c>
+      <c r="BS70" t="n">
+        <v>0.960445888374807</v>
+      </c>
+      <c r="BT70" t="n">
+        <v>13.89728103216176</v>
+      </c>
+      <c r="BU70" t="n">
+        <v>13.89728103216176</v>
+      </c>
+      <c r="BV70" t="n">
+        <v>0.960445888374807</v>
+      </c>
+      <c r="BW70" t="n">
+        <v>373.6972710510069</v>
+      </c>
+      <c r="BX70" t="n">
+        <v>-0.0636083086305867</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>16/04/2026 02:44:46</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>04-16_02-44-46_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r3.pkl</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>9</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G71" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>5</v>
+      </c>
+      <c r="K71" t="n">
+        <v>5</v>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M71" t="b">
+        <v>1</v>
+      </c>
+      <c r="N71" t="b">
+        <v>0</v>
+      </c>
+      <c r="O71" t="b">
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 3, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R71" t="n">
+        <v>1</v>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V71" t="n">
+        <v>3</v>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X71" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z71" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB71" t="inlineStr"/>
+      <c r="AC71" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE71" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG71" t="n">
+        <v>60</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ71" t="n">
+        <v>0.0532872336285395</v>
+      </c>
+      <c r="AK71" t="n">
+        <v>11.45074422183428</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>0.9656684043502372</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>-0.0116763416628604</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>18.48763907126751</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>0.9473809202088616</v>
+      </c>
+      <c r="AP71" t="n">
+        <v>18.48763907126751</v>
+      </c>
+      <c r="AQ71" t="n">
+        <v>18.48763907126751</v>
+      </c>
+      <c r="AR71" t="n">
+        <v>0.9473809202088616</v>
+      </c>
+      <c r="AS71" t="n">
+        <v>355.6809346892977</v>
+      </c>
+      <c r="AT71" t="n">
+        <v>-0.012330639431922</v>
+      </c>
+      <c r="AU71" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW71" t="inlineStr"/>
+      <c r="AX71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr"/>
+      <c r="BA71" t="inlineStr"/>
+      <c r="BB71" t="inlineStr"/>
+      <c r="BC71" t="inlineStr"/>
+      <c r="BD71" t="inlineStr"/>
+      <c r="BE71" t="inlineStr"/>
+      <c r="BF71" t="inlineStr"/>
+      <c r="BG71" t="inlineStr"/>
+      <c r="BH71" t="inlineStr"/>
+      <c r="BI71" t="inlineStr"/>
+      <c r="BJ71" t="inlineStr"/>
+      <c r="BK71" t="inlineStr"/>
+      <c r="BL71" t="inlineStr"/>
+      <c r="BM71" t="inlineStr"/>
+      <c r="BN71" t="inlineStr"/>
+      <c r="BO71" t="inlineStr"/>
+      <c r="BP71" t="inlineStr"/>
+      <c r="BQ71" t="inlineStr"/>
+      <c r="BR71" t="n">
+        <v>18.48763907126751</v>
+      </c>
+      <c r="BS71" t="n">
+        <v>0.9473809202088616</v>
+      </c>
+      <c r="BT71" t="n">
+        <v>18.48763907126751</v>
+      </c>
+      <c r="BU71" t="n">
+        <v>18.48763907126751</v>
+      </c>
+      <c r="BV71" t="n">
+        <v>0.9473809202088616</v>
+      </c>
+      <c r="BW71" t="n">
+        <v>355.6809346892977</v>
+      </c>
+      <c r="BX71" t="n">
+        <v>-0.012330639431922</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>16/04/2026 03:06:18</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>04-16_03-06-18_multihead_1heads_run0_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G72" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>5</v>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M72" t="b">
+        <v>1</v>
+      </c>
+      <c r="N72" t="b">
+        <v>0</v>
+      </c>
+      <c r="O72" t="b">
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R72" t="n">
+        <v>1</v>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V72" t="n">
+        <v>5</v>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X72" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z72" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB72" t="inlineStr"/>
+      <c r="AC72" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE72" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG72" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ72" t="n">
+        <v>0.0475144492153525</v>
+      </c>
+      <c r="AK72" t="n">
+        <v>14.06089642509881</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>0.957842651867185</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>-0.3548816273292907</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>16.18366865912141</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>0.9539384261448982</v>
+      </c>
+      <c r="AP72" t="n">
+        <v>16.18366865912141</v>
+      </c>
+      <c r="AQ72" t="n">
+        <v>16.18366865912141</v>
+      </c>
+      <c r="AR72" t="n">
+        <v>0.9539384261448982</v>
+      </c>
+      <c r="AS72" t="n">
+        <v>460.1217539143099</v>
+      </c>
+      <c r="AT72" t="n">
+        <v>-0.3095876217360449</v>
+      </c>
+      <c r="AU72" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW72" t="inlineStr"/>
+      <c r="AX72" t="inlineStr"/>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr"/>
+      <c r="BA72" t="inlineStr"/>
+      <c r="BB72" t="inlineStr"/>
+      <c r="BC72" t="inlineStr"/>
+      <c r="BD72" t="inlineStr"/>
+      <c r="BE72" t="inlineStr"/>
+      <c r="BF72" t="inlineStr"/>
+      <c r="BG72" t="inlineStr"/>
+      <c r="BH72" t="inlineStr"/>
+      <c r="BI72" t="inlineStr"/>
+      <c r="BJ72" t="inlineStr"/>
+      <c r="BK72" t="inlineStr"/>
+      <c r="BL72" t="inlineStr"/>
+      <c r="BM72" t="inlineStr"/>
+      <c r="BN72" t="inlineStr"/>
+      <c r="BO72" t="inlineStr"/>
+      <c r="BP72" t="inlineStr"/>
+      <c r="BQ72" t="inlineStr"/>
+      <c r="BR72" t="n">
+        <v>16.18366865912141</v>
+      </c>
+      <c r="BS72" t="n">
+        <v>0.9539384261448982</v>
+      </c>
+      <c r="BT72" t="n">
+        <v>16.18366865912141</v>
+      </c>
+      <c r="BU72" t="n">
+        <v>16.18366865912141</v>
+      </c>
+      <c r="BV72" t="n">
+        <v>0.9539384261448982</v>
+      </c>
+      <c r="BW72" t="n">
+        <v>460.1217539143099</v>
+      </c>
+      <c r="BX72" t="n">
+        <v>-0.3095876217360449</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>16/04/2026 03:20:20</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>04-16_03-20-20_multihead_1heads_run1_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G73" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" t="n">
+        <v>5</v>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M73" t="b">
+        <v>1</v>
+      </c>
+      <c r="N73" t="b">
+        <v>0</v>
+      </c>
+      <c r="O73" t="b">
+        <v>0</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R73" t="n">
+        <v>1</v>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V73" t="n">
+        <v>5</v>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X73" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA73" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE73" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG73" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH73" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI73" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ73" t="n">
+        <v>0.0475240840014234</v>
+      </c>
+      <c r="AK73" t="n">
+        <v>15.45087503110281</v>
+      </c>
+      <c r="AL73" t="n">
+        <v>0.9536752211274294</v>
+      </c>
+      <c r="AM73" t="n">
+        <v>-0.0755284449537923</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>16.22516671316922</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>0.9538203153678162</v>
+      </c>
+      <c r="AP73" t="n">
+        <v>16.22516671316922</v>
+      </c>
+      <c r="AQ73" t="n">
+        <v>16.22516671316922</v>
+      </c>
+      <c r="AR73" t="n">
+        <v>0.9538203153678162</v>
+      </c>
+      <c r="AS73" t="n">
+        <v>374.7415399291608</v>
+      </c>
+      <c r="AT73" t="n">
+        <v>-0.0665804819411519</v>
+      </c>
+      <c r="AU73" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV73" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr"/>
+      <c r="AX73" t="inlineStr"/>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr"/>
+      <c r="BA73" t="inlineStr"/>
+      <c r="BB73" t="inlineStr"/>
+      <c r="BC73" t="inlineStr"/>
+      <c r="BD73" t="inlineStr"/>
+      <c r="BE73" t="inlineStr"/>
+      <c r="BF73" t="inlineStr"/>
+      <c r="BG73" t="inlineStr"/>
+      <c r="BH73" t="inlineStr"/>
+      <c r="BI73" t="inlineStr"/>
+      <c r="BJ73" t="inlineStr"/>
+      <c r="BK73" t="inlineStr"/>
+      <c r="BL73" t="inlineStr"/>
+      <c r="BM73" t="inlineStr"/>
+      <c r="BN73" t="inlineStr"/>
+      <c r="BO73" t="inlineStr"/>
+      <c r="BP73" t="inlineStr"/>
+      <c r="BQ73" t="inlineStr"/>
+      <c r="BR73" t="n">
+        <v>16.22516671316922</v>
+      </c>
+      <c r="BS73" t="n">
+        <v>0.9538203153678162</v>
+      </c>
+      <c r="BT73" t="n">
+        <v>16.22516671316922</v>
+      </c>
+      <c r="BU73" t="n">
+        <v>16.22516671316922</v>
+      </c>
+      <c r="BV73" t="n">
+        <v>0.9538203153678162</v>
+      </c>
+      <c r="BW73" t="n">
+        <v>374.7415399291608</v>
+      </c>
+      <c r="BX73" t="n">
+        <v>-0.0665804819411519</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>16/04/2026 03:20:42</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>04-16_03-20-42_multihead_1heads_run2_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G74" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>5</v>
+      </c>
+      <c r="K74" t="n">
+        <v>5</v>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M74" t="b">
+        <v>1</v>
+      </c>
+      <c r="N74" t="b">
+        <v>0</v>
+      </c>
+      <c r="O74" t="b">
+        <v>0</v>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R74" t="n">
+        <v>1</v>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V74" t="n">
+        <v>5</v>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X74" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z74" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA74" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE74" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG74" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH74" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI74" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ74" t="n">
+        <v>0.0564142740490489</v>
+      </c>
+      <c r="AK74" t="n">
+        <v>19.52999871385854</v>
+      </c>
+      <c r="AL74" t="n">
+        <v>0.941445201648459</v>
+      </c>
+      <c r="AM74" t="n">
+        <v>-0.7885990562917138</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>22.39816390958793</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>0.9362508771731014</v>
+      </c>
+      <c r="AP74" t="n">
+        <v>22.39816390958793</v>
+      </c>
+      <c r="AQ74" t="n">
+        <v>22.39816390958793</v>
+      </c>
+      <c r="AR74" t="n">
+        <v>0.9362508771731014</v>
+      </c>
+      <c r="AS74" t="n">
+        <v>1527.647545835396</v>
+      </c>
+      <c r="AT74" t="n">
+        <v>-3.347954208602922</v>
+      </c>
+      <c r="AU74" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV74" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW74" t="inlineStr"/>
+      <c r="AX74" t="inlineStr"/>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr"/>
+      <c r="BA74" t="inlineStr"/>
+      <c r="BB74" t="inlineStr"/>
+      <c r="BC74" t="inlineStr"/>
+      <c r="BD74" t="inlineStr"/>
+      <c r="BE74" t="inlineStr"/>
+      <c r="BF74" t="inlineStr"/>
+      <c r="BG74" t="inlineStr"/>
+      <c r="BH74" t="inlineStr"/>
+      <c r="BI74" t="inlineStr"/>
+      <c r="BJ74" t="inlineStr"/>
+      <c r="BK74" t="inlineStr"/>
+      <c r="BL74" t="inlineStr"/>
+      <c r="BM74" t="inlineStr"/>
+      <c r="BN74" t="inlineStr"/>
+      <c r="BO74" t="inlineStr"/>
+      <c r="BP74" t="inlineStr"/>
+      <c r="BQ74" t="inlineStr"/>
+      <c r="BR74" t="n">
+        <v>22.39816390958793</v>
+      </c>
+      <c r="BS74" t="n">
+        <v>0.9362508771731014</v>
+      </c>
+      <c r="BT74" t="n">
+        <v>22.39816390958793</v>
+      </c>
+      <c r="BU74" t="n">
+        <v>22.39816390958793</v>
+      </c>
+      <c r="BV74" t="n">
+        <v>0.9362508771731014</v>
+      </c>
+      <c r="BW74" t="n">
+        <v>1527.647545835396</v>
+      </c>
+      <c r="BX74" t="n">
+        <v>-3.347954208602922</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>16/04/2026 03:25:49</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>04-16_03-25-49_multihead_1heads_run3_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>3</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>5</v>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M75" t="b">
+        <v>1</v>
+      </c>
+      <c r="N75" t="b">
+        <v>0</v>
+      </c>
+      <c r="O75" t="b">
+        <v>0</v>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V75" t="n">
+        <v>5</v>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X75" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z75" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE75" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG75" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ75" t="n">
+        <v>0.0434913845084939</v>
+      </c>
+      <c r="AK75" t="n">
+        <v>14.48083916563613</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>0.9565835804841486</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>-0.9376424149341448</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>16.77549481461656</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>0.9522539845794588</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>16.77549481461656</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>16.77549481461656</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>0.9522539845794588</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>679.6148164994199</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>-0.9343035700107424</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV75" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW75" t="inlineStr"/>
+      <c r="AX75" t="inlineStr"/>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr"/>
+      <c r="BA75" t="inlineStr"/>
+      <c r="BB75" t="inlineStr"/>
+      <c r="BC75" t="inlineStr"/>
+      <c r="BD75" t="inlineStr"/>
+      <c r="BE75" t="inlineStr"/>
+      <c r="BF75" t="inlineStr"/>
+      <c r="BG75" t="inlineStr"/>
+      <c r="BH75" t="inlineStr"/>
+      <c r="BI75" t="inlineStr"/>
+      <c r="BJ75" t="inlineStr"/>
+      <c r="BK75" t="inlineStr"/>
+      <c r="BL75" t="inlineStr"/>
+      <c r="BM75" t="inlineStr"/>
+      <c r="BN75" t="inlineStr"/>
+      <c r="BO75" t="inlineStr"/>
+      <c r="BP75" t="inlineStr"/>
+      <c r="BQ75" t="inlineStr"/>
+      <c r="BR75" t="n">
+        <v>16.77549481461656</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>0.9522539845794588</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>16.77549481461656</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>16.77549481461656</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>0.9522539845794588</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>679.6148164994199</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>-0.9343035700107424</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>16/04/2026 03:45:58</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>04-16_03-45-58_multihead_1heads_run4_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>4</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G76" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>5</v>
+      </c>
+      <c r="K76" t="n">
+        <v>5</v>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M76" t="b">
+        <v>1</v>
+      </c>
+      <c r="N76" t="b">
+        <v>0</v>
+      </c>
+      <c r="O76" t="b">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V76" t="n">
+        <v>5</v>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X76" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z76" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE76" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG76" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH76" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI76" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ76" t="n">
+        <v>0.0523850161795533</v>
+      </c>
+      <c r="AK76" t="n">
+        <v>16.2596596270809</v>
+      </c>
+      <c r="AL76" t="n">
+        <v>0.9512503249653153</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>-0.1797050658914036</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>20.15011187642431</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>0.9426492295452822</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>20.15011187642431</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>20.15011187642431</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>0.9426492295452822</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>416.0459387214829</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>-0.1841400820285408</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV76" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW76" t="inlineStr"/>
+      <c r="AX76" t="inlineStr"/>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr"/>
+      <c r="BA76" t="inlineStr"/>
+      <c r="BB76" t="inlineStr"/>
+      <c r="BC76" t="inlineStr"/>
+      <c r="BD76" t="inlineStr"/>
+      <c r="BE76" t="inlineStr"/>
+      <c r="BF76" t="inlineStr"/>
+      <c r="BG76" t="inlineStr"/>
+      <c r="BH76" t="inlineStr"/>
+      <c r="BI76" t="inlineStr"/>
+      <c r="BJ76" t="inlineStr"/>
+      <c r="BK76" t="inlineStr"/>
+      <c r="BL76" t="inlineStr"/>
+      <c r="BM76" t="inlineStr"/>
+      <c r="BN76" t="inlineStr"/>
+      <c r="BO76" t="inlineStr"/>
+      <c r="BP76" t="inlineStr"/>
+      <c r="BQ76" t="inlineStr"/>
+      <c r="BR76" t="n">
+        <v>20.15011187642431</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>0.9426492295452822</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>20.15011187642431</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>20.15011187642431</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>0.9426492295452822</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>416.0459387214829</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>-0.1841400820285408</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>16/04/2026 04:28:13</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>04-16_04-28-13_multihead_1heads_run5_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>5</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G77" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>5</v>
+      </c>
+      <c r="K77" t="n">
+        <v>5</v>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M77" t="b">
+        <v>1</v>
+      </c>
+      <c r="N77" t="b">
+        <v>0</v>
+      </c>
+      <c r="O77" t="b">
+        <v>0</v>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V77" t="n">
+        <v>5</v>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X77" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z77" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE77" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG77" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH77" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI77" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ77" t="n">
+        <v>0.0454845991199503</v>
+      </c>
+      <c r="AK77" t="n">
+        <v>18.32574302412092</v>
+      </c>
+      <c r="AL77" t="n">
+        <v>0.9450557983571134</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>-0.14442421302849</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>18.6126619143856</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>0.947025083158366</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>18.6126619143856</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>18.6126619143856</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>0.947025083158366</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>394.2664451642042</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>-0.1221518040832998</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV77" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW77" t="inlineStr"/>
+      <c r="AX77" t="inlineStr"/>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr"/>
+      <c r="BA77" t="inlineStr"/>
+      <c r="BB77" t="inlineStr"/>
+      <c r="BC77" t="inlineStr"/>
+      <c r="BD77" t="inlineStr"/>
+      <c r="BE77" t="inlineStr"/>
+      <c r="BF77" t="inlineStr"/>
+      <c r="BG77" t="inlineStr"/>
+      <c r="BH77" t="inlineStr"/>
+      <c r="BI77" t="inlineStr"/>
+      <c r="BJ77" t="inlineStr"/>
+      <c r="BK77" t="inlineStr"/>
+      <c r="BL77" t="inlineStr"/>
+      <c r="BM77" t="inlineStr"/>
+      <c r="BN77" t="inlineStr"/>
+      <c r="BO77" t="inlineStr"/>
+      <c r="BP77" t="inlineStr"/>
+      <c r="BQ77" t="inlineStr"/>
+      <c r="BR77" t="n">
+        <v>18.6126619143856</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>0.947025083158366</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>18.6126619143856</v>
+      </c>
+      <c r="BU77" t="n">
+        <v>18.6126619143856</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>0.947025083158366</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>394.2664451642042</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>-0.1221518040832998</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>16/04/2026 04:46:45</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>04-16_04-46-45_multihead_1heads_run6_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>6</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G78" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>5</v>
+      </c>
+      <c r="K78" t="n">
+        <v>5</v>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M78" t="b">
+        <v>1</v>
+      </c>
+      <c r="N78" t="b">
+        <v>0</v>
+      </c>
+      <c r="O78" t="b">
+        <v>0</v>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V78" t="n">
+        <v>5</v>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X78" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z78" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD78" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE78" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG78" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH78" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI78" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ78" t="n">
+        <v>0.0475478690488842</v>
+      </c>
+      <c r="AK78" t="n">
+        <v>18.49291590390904</v>
+      </c>
+      <c r="AL78" t="n">
+        <v>0.9445545810037864</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>-0.2297224710304075</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>25.54202595043733</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>0.9273028916059836</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>25.54202595043733</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>25.54202595043733</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>0.9273028916059836</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>438.6751398054765</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>-0.2485467773809473</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV78" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW78" t="inlineStr"/>
+      <c r="AX78" t="inlineStr"/>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr"/>
+      <c r="BA78" t="inlineStr"/>
+      <c r="BB78" t="inlineStr"/>
+      <c r="BC78" t="inlineStr"/>
+      <c r="BD78" t="inlineStr"/>
+      <c r="BE78" t="inlineStr"/>
+      <c r="BF78" t="inlineStr"/>
+      <c r="BG78" t="inlineStr"/>
+      <c r="BH78" t="inlineStr"/>
+      <c r="BI78" t="inlineStr"/>
+      <c r="BJ78" t="inlineStr"/>
+      <c r="BK78" t="inlineStr"/>
+      <c r="BL78" t="inlineStr"/>
+      <c r="BM78" t="inlineStr"/>
+      <c r="BN78" t="inlineStr"/>
+      <c r="BO78" t="inlineStr"/>
+      <c r="BP78" t="inlineStr"/>
+      <c r="BQ78" t="inlineStr"/>
+      <c r="BR78" t="n">
+        <v>25.54202595043733</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>0.9273028916059836</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>25.54202595043733</v>
+      </c>
+      <c r="BU78" t="n">
+        <v>25.54202595043733</v>
+      </c>
+      <c r="BV78" t="n">
+        <v>0.9273028916059836</v>
+      </c>
+      <c r="BW78" t="n">
+        <v>438.6751398054765</v>
+      </c>
+      <c r="BX78" t="n">
+        <v>-0.2485467773809473</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>16/04/2026 04:48:01</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>04-16_04-48-01_multihead_1heads_run7_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>7</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G79" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>5</v>
+      </c>
+      <c r="K79" t="n">
+        <v>5</v>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M79" t="b">
+        <v>1</v>
+      </c>
+      <c r="N79" t="b">
+        <v>0</v>
+      </c>
+      <c r="O79" t="b">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V79" t="n">
+        <v>5</v>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X79" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z79" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD79" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE79" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG79" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH79" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI79" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ79" t="n">
+        <v>0.042665844382621</v>
+      </c>
+      <c r="AK79" t="n">
+        <v>14.2755415205057</v>
+      </c>
+      <c r="AL79" t="n">
+        <v>0.9571991034234372</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>-0.8699873932569235</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>18.85004114791637</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>0.9463494600146124</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>18.85004114791637</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>18.85004114791637</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>0.9463494600146124</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>643.830614843066</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>-0.8324554240706681</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV79" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW79" t="inlineStr"/>
+      <c r="AX79" t="inlineStr"/>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr"/>
+      <c r="BA79" t="inlineStr"/>
+      <c r="BB79" t="inlineStr"/>
+      <c r="BC79" t="inlineStr"/>
+      <c r="BD79" t="inlineStr"/>
+      <c r="BE79" t="inlineStr"/>
+      <c r="BF79" t="inlineStr"/>
+      <c r="BG79" t="inlineStr"/>
+      <c r="BH79" t="inlineStr"/>
+      <c r="BI79" t="inlineStr"/>
+      <c r="BJ79" t="inlineStr"/>
+      <c r="BK79" t="inlineStr"/>
+      <c r="BL79" t="inlineStr"/>
+      <c r="BM79" t="inlineStr"/>
+      <c r="BN79" t="inlineStr"/>
+      <c r="BO79" t="inlineStr"/>
+      <c r="BP79" t="inlineStr"/>
+      <c r="BQ79" t="inlineStr"/>
+      <c r="BR79" t="n">
+        <v>18.85004114791637</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>0.9463494600146124</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>18.85004114791637</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>18.85004114791637</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>0.9463494600146124</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>643.830614843066</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>-0.8324554240706681</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>16/04/2026 04:48:32</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>04-16_04-48-32_multihead_1heads_run8_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>8</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Final (Last Iteration)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G80" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>5</v>
+      </c>
+      <c r="K80" t="n">
+        <v>5</v>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M80" t="b">
+        <v>1</v>
+      </c>
+      <c r="N80" t="b">
+        <v>0</v>
+      </c>
+      <c r="O80" t="b">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V80" t="n">
+        <v>5</v>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X80" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z80" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD80" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE80" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG80" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>0.0505677216334654</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>17.59279548502038</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>0.9472533200253476</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>-0.5436211648856226</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>20.48278034811164</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>0.9417023964321825</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>20.48278034811164</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>20.48278034811164</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>0.9417023964321825</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>524.0942034894714</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>-0.4916644902671661</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV80" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW80" t="inlineStr"/>
+      <c r="AX80" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr"/>
+      <c r="BA80" t="inlineStr"/>
+      <c r="BB80" t="inlineStr"/>
+      <c r="BC80" t="inlineStr"/>
+      <c r="BD80" t="inlineStr"/>
+      <c r="BE80" t="inlineStr"/>
+      <c r="BF80" t="inlineStr"/>
+      <c r="BG80" t="inlineStr"/>
+      <c r="BH80" t="inlineStr"/>
+      <c r="BI80" t="inlineStr"/>
+      <c r="BJ80" t="inlineStr"/>
+      <c r="BK80" t="inlineStr"/>
+      <c r="BL80" t="inlineStr"/>
+      <c r="BM80" t="inlineStr"/>
+      <c r="BN80" t="inlineStr"/>
+      <c r="BO80" t="inlineStr"/>
+      <c r="BP80" t="inlineStr"/>
+      <c r="BQ80" t="inlineStr"/>
+      <c r="BR80" t="n">
+        <v>20.48278034811164</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>0.9417023964321825</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>20.48278034811164</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>20.48278034811164</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>0.9417023964321825</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>524.0942034894714</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>-0.4916644902671661</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>16/04/2026 05:04:22</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>04-16_05-04-22_multihead_1heads_run9_spsa_serial_f5_w5_h5_effsu2_lin_r5.pkl</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>9</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Best (Lowest Val Loss)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>data/reduce_row_number_absolutes</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>16590</v>
+      </c>
+      <c r="G81" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>['ya', 'yr', 'wv']</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>['Yaw Angle']</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>5</v>
+      </c>
+      <c r="K81" t="n">
+        <v>5</v>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+      <c r="M81" t="b">
+        <v>1</v>
+      </c>
+      <c r="N81" t="b">
+        <v>0</v>
+      </c>
+      <c r="O81" t="b">
+        <v>0</v>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>multihead</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>[{'features': ['ya', 'yr', 'wv'], 'output_dim': 1, 'reps': 5, 'encoding': 'serial', 'ansatz': 'effsu2', 'entangle': 'lin', 'map': [0, 1, 2]}]</t>
+        </is>
+      </c>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>serial</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>effsu2</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>lin</t>
+        </is>
+      </c>
+      <c r="V81" t="n">
+        <v>5</v>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>[0, 1, 2]</t>
+        </is>
+      </c>
+      <c r="X81" t="b">
+        <v>0</v>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>spsa</t>
+        </is>
+      </c>
+      <c r="Z81" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>4000</v>
+      </c>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="n">
+        <v>256</v>
+      </c>
+      <c r="AD81" t="inlineStr">
+        <is>
+          <t>[0.1, 0.001]</t>
+        </is>
+      </c>
+      <c r="AE81" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>[1.0, 1.0, 1.0, 1.0]</t>
+        </is>
+      </c>
+      <c r="AG81" t="n">
+        <v>80</v>
+      </c>
+      <c r="AH81" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI81" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ81" t="n">
+        <v>0.0553272979880106</v>
+      </c>
+      <c r="AK81" t="n">
+        <v>22.6303529381066</v>
+      </c>
+      <c r="AL81" t="n">
+        <v>0.9321497265652798</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>-0.7048243260929086</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>24.02794679128497</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>0.9316122277942562</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>24.02794679128497</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>24.02794679128497</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>0.9316122277942562</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>566.7195448855887</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>-0.6129837258602395</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AV81" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr"/>
+      <c r="AX81" t="inlineStr"/>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr"/>
+      <c r="BA81" t="inlineStr"/>
+      <c r="BB81" t="inlineStr"/>
+      <c r="BC81" t="inlineStr"/>
+      <c r="BD81" t="inlineStr"/>
+      <c r="BE81" t="inlineStr"/>
+      <c r="BF81" t="inlineStr"/>
+      <c r="BG81" t="inlineStr"/>
+      <c r="BH81" t="inlineStr"/>
+      <c r="BI81" t="inlineStr"/>
+      <c r="BJ81" t="inlineStr"/>
+      <c r="BK81" t="inlineStr"/>
+      <c r="BL81" t="inlineStr"/>
+      <c r="BM81" t="inlineStr"/>
+      <c r="BN81" t="inlineStr"/>
+      <c r="BO81" t="inlineStr"/>
+      <c r="BP81" t="inlineStr"/>
+      <c r="BQ81" t="inlineStr"/>
+      <c r="BR81" t="n">
+        <v>24.02794679128497</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>0.9316122277942562</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>24.02794679128497</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>24.02794679128497</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>0.9316122277942562</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>566.7195448855887</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>-0.6129837258602395</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
